--- a/data/trans_orig/IP16A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Clase-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13248</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33995</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>33259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71945</t>
+          <t>71482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103898</t>
+          <t>104766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129538</t>
+          <t>129161</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134626</t>
+          <t>134620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>236948</t>
+          <t>237039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243643</t>
+          <t>243632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21181</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48569</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37179</t>
+          <t>37281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>56625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69699</t>
+          <t>69612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>128915</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,77 +5445,77 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>604</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5487</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6307</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6238</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>175105</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,77 +5553,77 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>177063</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>173449</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>178332</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,93%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>354690</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>350883</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>356559</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>98,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>177063</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>173921</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>178333</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>354690</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>350952</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>356559</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51861</t>
+          <t>52194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94973</t>
+          <t>94682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32534</t>
+          <t>33045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>26835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>61778</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>148484</t>
+          <t>147732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>154945</t>
+          <t>154923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>135406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>285922</t>
+          <t>286739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294073</t>
+          <t>294117</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A04-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>813</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>813</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4189</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3946</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3471</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17044</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13221</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17044</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13668</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>33341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4341</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,81%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4993</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36249</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33259</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33344</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,19%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,48%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>112</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71482</t>
+          <t>71662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1371</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4264</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22528</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19721</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>82,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22528</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>19183</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38488</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6523</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1436</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4968</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6136</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>133113</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>128774</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134622</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>108298</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>104766</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>104712</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>133113</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>129161</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134620</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>363</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237039</t>
+          <t>236913</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>243632</t>
+          <t>243683</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>625</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>625</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3216</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>625</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3217</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24328</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22394</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24328</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21737</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48540</t>
+          <t>48549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2760</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3252</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>18,52%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3239</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14260</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10880</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14260</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>12141</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>37268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4391,102 +4391,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3122</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3141</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4316</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72146</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>59850</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>56625</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>56711</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>72146</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>69612</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>187</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128915</t>
+          <t>129148</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72753</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72753</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37598</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>11795</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1873</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>177063</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>173349</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>178323</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>177627</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>175114</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>175093</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,24%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>177063</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>173449</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>178332</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>506</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>350883</t>
+          <t>351072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>356559</t>
+          <t>356567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>178936</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>178936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>727</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3853</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3561</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -6105,74 +6105,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18272</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15558</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15146</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>81,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>58</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>36466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6796,42 +6796,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6909,52 +6909,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4367</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1389</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4876</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>55172</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52194</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52103</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,12%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>149</t>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94682</t>
+          <t>94453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7369,102 +7369,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2734</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2674</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3410</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4245</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -7477,74 +7477,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29593</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26976</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35243</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33045</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33105</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,53%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29593</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>26835</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>88,73%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>93</t>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>61967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,107 +7707,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4152</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>10,56%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3975</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4920</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>32,89%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2093</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5285</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -7820,107 +7820,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11369</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>11649</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8873</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>8898</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>89,44%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11369</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>8111</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>67,11%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>23018</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>20191</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>25111</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>80,41%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>23018</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>19826</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>24500</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>78,95%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>4028</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1454</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>8645</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8541</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>139024</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>135443</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>152349</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>147732</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>154923</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>147836</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>154880</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>97,42%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>139024</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>135406</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>286739</t>
+          <t>286434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294117</t>
+          <t>294166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
